--- a/results/pilot_b_results.xlsx
+++ b/results/pilot_b_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="178">
   <si>
     <t xml:space="preserve">Pilot B: two LG M50 cells, resolved against lumped neighbour. Repository github.com/siddharth161204-wq/m50-two-cell-pilot</t>
   </si>
@@ -413,31 +413,46 @@
     <t xml:space="preserve">V2 median case, mesh refined: change in resolved mean peak (K)</t>
   </si>
   <si>
-    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s): largest change in a hottest-point crossing time (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s): change in resolved max peak (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s): change in resolved mean peak (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s): largest change in a hottest-point crossing time (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s): change in resolved max peak (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s): change in resolved mean peak (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes): largest change in a hottest-point crossing time (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes): change in resolved max peak (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes): change in resolved mean peak (K)</t>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): largest change in a hottest-point crossing time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): change in resolved max peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): change in resolved mean peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): largest change in a hottest-point crossing time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): change in resolved max peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): change in resolved mean peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): largest change in a hottest-point crossing time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): change in resolved max peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): change in resolved mean peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrounded rerun of the base case (v2_max_tau10_G0.5_refine1_dt0.1): crossing times agree with the sweep table to its 0.01 s rounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrounded rerun of the base case (v2_max_tau30_G0.5_refine1_dt0.1): crossing times agree with the sweep table to its 0.01 s rounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rerun of two_E33223_tau30_G0.5 with the final code: fields differing from the registered row, run time excepted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rerun of two_E33223_tau30_G0.5 with the final code: largest difference in any recorded time series</t>
   </si>
   <si>
     <t xml:space="preserve">V3 median case: lumped peak (C)</t>
@@ -552,10 +567,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0E+00"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -649,7 +665,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -671,6 +687,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7179,7 +7199,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -7206,7 +7226,7 @@
       <c r="A3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>2.32108658728963E-011</v>
       </c>
     </row>
@@ -7247,7 +7267,7 @@
         <v>128</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.00852537864319203</v>
+        <v>0.00503790786554426</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,7 +7275,7 @@
         <v>129</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.0660429477791809</v>
+        <v>0.062616266371947</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7263,7 +7283,7 @@
         <v>130</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.00840811591859847</v>
+        <v>0.00548299125347285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7271,7 +7291,7 @@
         <v>131</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.00655299228777651</v>
+        <v>0.00327365881429564</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7279,7 +7299,7 @@
         <v>132</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.0429347092829744</v>
+        <v>0.0398145369898657</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7287,7 +7307,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.00244141162710321</v>
+        <v>0.00551631911679351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7295,7 +7315,7 @@
         <v>134</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.082624638350179</v>
+        <v>0.0847956586240528</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7303,7 +7323,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.41400485393564</v>
+        <v>1.41088468164253</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7311,54 +7331,86 @@
         <v>136</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.310936382973068</v>
+        <v>-0.307861475483378</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>85.700699276118</v>
+      <c r="B17" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>82.9629522175588</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>96.718297592367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.2E-011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.308102760535576</v>
+        <v>85.700699276118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22" s="2" t="n">
+        <v>82.9629522175588</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>96.718297592367</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1.2E-011</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.308102760535576</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>0.169868364338555</v>
       </c>
     </row>
@@ -7399,7 +7451,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -7411,37 +7463,37 @@
         <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>26</v>
@@ -7449,7 +7501,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>33222.9</v>
@@ -7499,7 +7551,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>33222.9</v>
@@ -7549,7 +7601,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>21495.3</v>
@@ -7579,7 +7631,7 @@
         <v>134.023204376743</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>152.8</v>
@@ -7599,7 +7651,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>33222.9</v>
@@ -7629,7 +7681,7 @@
         <v>153.92403509182</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>168.9</v>
@@ -7649,7 +7701,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>33222.9</v>
@@ -7699,7 +7751,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
@@ -7711,27 +7763,27 @@
         <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>33222.9</v>
@@ -7742,28 +7794,28 @@
       <c r="D10" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>39.4372585838387</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>5.70230308629154</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>2.54228147539589</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <v>0.464784237905866</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="6" t="n">
         <v>16.9768730494089</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>24.9770892950197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>21495.3</v>
@@ -7774,28 +7826,28 @@
       <c r="D11" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>0.556888327919477</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>0.373256864797872</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>0.195812568197149</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="6" t="n">
         <v>22.9911075058746</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>33222.9</v>
@@ -7806,28 +7858,28 @@
       <c r="D12" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>0.908874182659571</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>0.514565682603055</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>0.283055000975135</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <v>23.9667529712611</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>21495.3</v>
@@ -7838,28 +7890,28 @@
       <c r="D13" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>0.00565241433061335</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>33222.9</v>
@@ -7870,28 +7922,28 @@
       <c r="D14" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="6" t="n">
         <v>0.00735722463359847</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>33222.9</v>
@@ -7902,28 +7954,28 @@
       <c r="D15" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>34.4537315506632</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>5.36641142272815</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>2.45736267961699</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="6" t="n">
         <v>0.502713407094315</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="6" t="n">
         <v>6.45239521409972</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="6" t="n">
         <v>11.6478170961914</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>33222.9</v>
@@ -7934,28 +7986,28 @@
       <c r="D16" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
         <v>0.887488878554445</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>0.50490658607203</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>0.251684565516942</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <v>10.4706385650631</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>21495.3</v>
@@ -7966,23 +8018,23 @@
       <c r="D17" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>0.589585671823979</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>0.398408667801335</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>0.208437662459761</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="6" t="n">
         <v>8.84197793287098</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/results/pilot_b_results.xlsx
+++ b/results/pilot_b_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="181">
   <si>
     <t xml:space="preserve">Pilot B: two LG M50 cells, resolved against lumped neighbour. Repository github.com/siddharth161204-wq/m50-two-cell-pilot</t>
   </si>
@@ -420,6 +420,15 @@
   </si>
   <si>
     <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): change in resolved mean peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): largest change in a hottest-point crossing time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): change in resolved max peak (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 max energy, tau 10 s, 500 mW/K, mesh refined (297,057 nodes) (against an unrounded base run): change in resolved mean peak (K)</t>
   </si>
   <si>
     <t xml:space="preserve">V2 max energy, tau 30 s, 500 mW/K, time step halved (0.05 s) (against an unrounded base run): largest change in a hottest-point crossing time (s)</t>
@@ -7199,7 +7208,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -7291,7 +7300,7 @@
         <v>131</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.00327365881429564</v>
+        <v>0.0200216726846616</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7299,7 +7308,7 @@
         <v>132</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.0398145369898657</v>
+        <v>1.48897783640496</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7307,7 +7316,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.00551631911679351</v>
+        <v>-0.305821865303415</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7315,7 +7324,7 @@
         <v>134</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.0847956586240528</v>
+        <v>0.00327365881429564</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7323,7 +7332,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.41088468164253</v>
+        <v>0.0398145369898657</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7331,47 +7340,47 @@
         <v>136</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.307861475483378</v>
+        <v>0.00551631911679351</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>138</v>
+      <c r="B17" s="2" t="n">
+        <v>0.0847956586240528</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="2" t="s">
         <v>138</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1.41088468164253</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0</v>
+        <v>-0.307861475483378</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>85.700699276118</v>
+      <c r="B21" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7379,7 +7388,7 @@
         <v>143</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>82.9629522175588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,15 +7396,15 @@
         <v>144</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>96.718297592367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>1.2E-011</v>
+      <c r="B24" s="2" t="n">
+        <v>85.700699276118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7403,7 +7412,7 @@
         <v>146</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.308102760535576</v>
+        <v>82.9629522175588</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7411,6 +7420,30 @@
         <v>147</v>
       </c>
       <c r="B26" s="2" t="n">
+        <v>96.718297592367</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1.2E-011</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.308102760535576</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>0.169868364338555</v>
       </c>
     </row>
@@ -7451,7 +7484,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -7463,37 +7496,37 @@
         <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>26</v>
@@ -7501,7 +7534,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>33222.9</v>
@@ -7551,7 +7584,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>33222.9</v>
@@ -7601,7 +7634,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>21495.3</v>
@@ -7631,7 +7664,7 @@
         <v>134.023204376743</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>152.8</v>
@@ -7651,7 +7684,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>33222.9</v>
@@ -7681,7 +7714,7 @@
         <v>153.92403509182</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>168.9</v>
@@ -7701,7 +7734,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>33222.9</v>
@@ -7751,7 +7784,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
@@ -7763,27 +7796,27 @@
         <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>33222.9</v>
@@ -7815,7 +7848,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>21495.3</v>
@@ -7842,12 +7875,12 @@
         <v>22.9911075058746</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>33222.9</v>
@@ -7874,12 +7907,12 @@
         <v>23.9667529712611</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>21495.3</v>
@@ -7903,15 +7936,15 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>33222.9</v>
@@ -7935,15 +7968,15 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>33222.9</v>
@@ -7975,7 +8008,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>33222.9</v>
@@ -8002,12 +8035,12 @@
         <v>10.4706385650631</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>21495.3</v>
@@ -8034,7 +8067,7 @@
         <v>8.84197793287098</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
